--- a/output/cities.xlsx
+++ b/output/cities.xlsx
@@ -6,14 +6,14 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Source Cities" r:id="rId3" sheetId="1"/>
-    <sheet name="Destination Cities" r:id="rId4" sheetId="2"/>
+    <sheet name="Source Cities" r:id="rId5" sheetId="17"/>
+    <sheet name="Destination Cities" r:id="rId4" sheetId="18"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="146">
   <si>
     <t>City Code</t>
   </si>
@@ -274,6 +274,183 @@
   </si>
   <si>
     <t>Dubai International</t>
+  </si>
+  <si>
+    <t>IXX</t>
+  </si>
+  <si>
+    <t>Bidar Airport</t>
+  </si>
+  <si>
+    <t>KJB</t>
+  </si>
+  <si>
+    <t>Kurnool Airport</t>
+  </si>
+  <si>
+    <t>HBX</t>
+  </si>
+  <si>
+    <t>Hubli, India</t>
+  </si>
+  <si>
+    <t>Hubli Airport</t>
+  </si>
+  <si>
+    <t>HJR</t>
+  </si>
+  <si>
+    <t>Khajuraho, India</t>
+  </si>
+  <si>
+    <t>Khajuraho Airport</t>
+  </si>
+  <si>
+    <t>HRK</t>
+  </si>
+  <si>
+    <t>Kharkov, Ukraine</t>
+  </si>
+  <si>
+    <t>Kharkov</t>
+  </si>
+  <si>
+    <t>HIR</t>
+  </si>
+  <si>
+    <t>Honiara, Solomon Islands</t>
+  </si>
+  <si>
+    <t>Henderson International</t>
+  </si>
+  <si>
+    <t>HHQ</t>
+  </si>
+  <si>
+    <t>Hua Hin, Thailand</t>
+  </si>
+  <si>
+    <t>Hua Hin Airport</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>Harlingen, United States</t>
+  </si>
+  <si>
+    <t>Valley International-TX</t>
+  </si>
+  <si>
+    <t>HLH</t>
+  </si>
+  <si>
+    <t>Ulanhot, China</t>
+  </si>
+  <si>
+    <t>Ulanhot</t>
+  </si>
+  <si>
+    <t>HSR</t>
+  </si>
+  <si>
+    <t>Rajkot, India</t>
+  </si>
+  <si>
+    <t>Rajkot International Airport</t>
+  </si>
+  <si>
+    <t>TIR</t>
+  </si>
+  <si>
+    <t>Tirupati Airport</t>
+  </si>
+  <si>
+    <t>PNY</t>
+  </si>
+  <si>
+    <t>Puducherry Airport</t>
+  </si>
+  <si>
+    <t>MYQ</t>
+  </si>
+  <si>
+    <t>Mysore, India</t>
+  </si>
+  <si>
+    <t>Mysore Airport</t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>Milan, Italy</t>
+  </si>
+  <si>
+    <t>All airports of Milan</t>
+  </si>
+  <si>
+    <t>MXP</t>
+  </si>
+  <si>
+    <t>Malpensa</t>
+  </si>
+  <si>
+    <t>MYR</t>
+  </si>
+  <si>
+    <t>Myrtle Beach, United States</t>
+  </si>
+  <si>
+    <t>All airports of Myrtle Beach</t>
+  </si>
+  <si>
+    <t>MCO</t>
+  </si>
+  <si>
+    <t>Orlando, United States</t>
+  </si>
+  <si>
+    <t>Orlando-FL</t>
+  </si>
+  <si>
+    <t>MDA</t>
+  </si>
+  <si>
+    <t>Mundra, India</t>
+  </si>
+  <si>
+    <t>Mundra Airport</t>
+  </si>
+  <si>
+    <t>MUX</t>
+  </si>
+  <si>
+    <t>Multan, Pakistan</t>
+  </si>
+  <si>
+    <t>Multan</t>
+  </si>
+  <si>
+    <t>MLI</t>
+  </si>
+  <si>
+    <t>Moline, United States</t>
+  </si>
+  <si>
+    <t>Quad-City-IL</t>
+  </si>
+  <si>
+    <t>MGA</t>
+  </si>
+  <si>
+    <t>Managua, Nicaragua</t>
+  </si>
+  <si>
+    <t>Managua International</t>
+  </si>
+  <si>
+    <t>Ghaziabad, India</t>
   </si>
 </sst>
 </file>
@@ -316,9 +493,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -477,90 +654,255 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>44</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>47</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>50</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>54</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>56</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>59</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -568,9 +910,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -696,178 +1038,244 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>9</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>11</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>14</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>17</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>20</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>23</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>26</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>29</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>35</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>38</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>52</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>54</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>56</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>59</v>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
